--- a/output/pdf_financials_xlsx/MGG.xlsx
+++ b/output/pdf_financials_xlsx/MGG.xlsx
@@ -4533,40 +4533,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.785617</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.12057</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.243535</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.360706</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.438074</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.367771</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.838779</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.521755</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>7.291731</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>9.211259</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>9.568441999999999</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>10.044419</v>
       </c>
     </row>
     <row r="93">
@@ -7768,7 +7768,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>1.785617</v>
       </c>
@@ -8940,7 +8944,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MGG.xlsx
+++ b/output/pdf_financials_xlsx/MGG.xlsx
@@ -885,34 +885,34 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.052387</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.082291</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.09352100000000001</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.150255</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.08155999999999999</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.018533</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.036378</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.03111</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.012862</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.102382</v>
       </c>
     </row>
     <row r="13">
@@ -1588,34 +1588,34 @@
         <v>-1.189391</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.523401</v>
+        <v>-1.575788</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.296065</v>
+        <v>-2.378356</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.67801</v>
+        <v>-3.771531</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-5.465645</v>
+        <v>-5.6159</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-5.373809</v>
+        <v>-5.455369</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-7.520677</v>
+        <v>-7.53921</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-6.575644</v>
+        <v>-6.612022</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-7.688889</v>
+        <v>-7.719999</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-3.776462</v>
+        <v>-3.789324</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-5.665405</v>
+        <v>-5.767787</v>
       </c>
     </row>
     <row r="28">
@@ -1674,34 +1674,34 @@
         <v>-1.189391</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.523401</v>
+        <v>-1.575788</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.296065</v>
+        <v>-2.378356</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.67801</v>
+        <v>-3.771531</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-5.465645</v>
+        <v>-5.6159</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-5.373809</v>
+        <v>-5.455369</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-7.520677</v>
+        <v>-7.53921</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-6.575644</v>
+        <v>-6.612022</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-7.688889</v>
+        <v>-7.719999</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.776462</v>
+        <v>-3.789324</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-5.665405</v>
+        <v>-5.767787</v>
       </c>
     </row>
     <row r="30">
@@ -1895,40 +1895,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.457522</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.346273</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.264014</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.641026</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.791516</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>7.597059</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.449527</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>4.102028</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>6.31623</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.503938</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.6173</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.148787</v>
       </c>
     </row>
     <row r="35">
@@ -1981,40 +1981,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.457522</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.346273</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>3.264014</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.641026</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.791516</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>7.597059</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.449527</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>4.102028</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>2.442175</v>
+        <v>8.758405</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.396853</v>
+        <v>1.900791</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.122109</v>
+        <v>0.739409</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.057815</v>
+        <v>1.206602</v>
       </c>
     </row>
     <row r="37">
@@ -2497,40 +2497,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.470844</v>
+        <v>0.013322</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.35397</v>
+        <v>0.007697</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.328999</v>
+        <v>1.064985</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.692342</v>
+        <v>0.051316</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.836949</v>
+        <v>0.045433</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>7.651039</v>
+        <v>0.05398</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.574036</v>
+        <v>0.124509</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>4.248923</v>
+        <v>0.146895</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>6.423146</v>
+        <v>0.106916</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.611838</v>
+        <v>0.1079</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.688279</v>
+        <v>0.070979</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.219247</v>
+        <v>0.07045999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -35474,7 +35474,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">

--- a/output/pdf_financials_xlsx/MGG.xlsx
+++ b/output/pdf_financials_xlsx/MGG.xlsx
@@ -685,19 +685,19 @@
         <v>0.411918</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.530451</v>
+        <v>0.563784</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.495126</v>
+        <v>0.590459</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.446867</v>
+        <v>0.526867</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.3878</v>
+        <v>0.469467</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.411507</v>
+        <v>0.476507</v>
       </c>
     </row>
     <row r="8">
@@ -814,10 +814,10 @@
         <v>0.411918</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.530451</v>
+        <v>0.563784</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.495126</v>
+        <v>0.590459</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>5.674677</v>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -32976,7 +32976,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E356" s="5" t="n">
         <v>0.201</v>
       </c>
@@ -33128,7 +33132,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E358" s="5" t="n">
         <v>0.007</v>
       </c>
@@ -34850,7 +34858,11 @@
           <t>Directors' fees (Note 7)</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr">
         <is>
           <t>-</t>
@@ -36952,7 +36964,11 @@
           <t>Deferred income tax recovery (Note 11)</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
